--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.75320411011123</v>
+        <v>4.672395667893075</v>
       </c>
       <c r="D2" t="n">
-        <v>20.50162263026598</v>
+        <v>3.331513677418223</v>
       </c>
       <c r="E2" t="n">
-        <v>4.050599695029121</v>
+        <v>0.6582224504422318</v>
       </c>
       <c r="F2" t="n">
-        <v>6.889885528465751</v>
+        <v>1.119606398375685</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.85440350016947</v>
+        <v>5.988840568777539</v>
       </c>
       <c r="D3" t="n">
-        <v>34.28139368719749</v>
+        <v>5.570726474169592</v>
       </c>
       <c r="E3" t="n">
-        <v>4.050599695029121</v>
+        <v>0.6582224504422318</v>
       </c>
       <c r="F3" t="n">
-        <v>6.889885528465751</v>
+        <v>1.119606398375685</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
